--- a/onagawa/output/女川町_水道_数値定義と確定値一覧.xlsx
+++ b/onagawa/output/女川町_水道_数値定義と確定値一覧.xlsx
@@ -11,7 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_確定値一覧_R7決算" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_指標の算式と値" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_有収水量推計の見直し" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_総括原価の再計算" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_総括原価の検証と再計算" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_原資料の要修正箇所" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -141,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -242,17 +243,26 @@
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2538,505 +2548,1006 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="54" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>４　総括原価の再計算　－　控除項目に論点</t>
+          <t>４　総括原価の検証と再計算</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>引継ぎメモ記載の費目（令和８〜12年度の5年計）に基づく再計算。原資料の確認が必要</t>
+          <t>原資料：onagawa_tariff_cost_calc.xlsx ②総括原価の算定／onagawa_cost_sim_v1.xlsx／経営戦略試算シート【成行】財政シミュ</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■【重要】長期前受金戻入益の控除額</t>
+          <t>■　(1) 財政シミュとの照合　－　長期前受金戻入益だけが未反映</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>区　分</t>
+          <t>費　目</t>
         </is>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>5年計（千円）</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>年平均（千円）</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>対比</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>根　拠</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>引継ぎメモの控除額</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="n">
-        <v>-450000</v>
-      </c>
-      <c r="C6" s="20" t="n">
-        <v>-90000</v>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>「推計値・要確定後更新」と記載されている</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>★令和７年度実績ベース</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="n">
-        <v>-1671262</v>
-      </c>
-      <c r="C7" s="31" t="n">
-        <v>-334252</v>
-      </c>
-      <c r="D7" s="23" t="inlineStr">
-        <is>
-          <t>3.7倍</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>令和７年度実績334,252,462円×5年。未収益化残高7,491,683千円に対し年334,252千円なので、今後20年以上この水準が続く</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>★ 控除額が3.7倍違うため、総括原価はほぼ倍の差が出ます。原資料（onagawa_cost_sim_v1.xlsx 等）での確認が最優先です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>■　総括原価（5年計・千円）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>費　目</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>引継ぎメモ</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>★実績ベースに是正</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>差</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+          <t>R11</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>R12</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>5年計</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>照合結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>維持管理費（営業費用−減価償却費）</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>131926</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>133182</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>134453</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>135742</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>137024</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>672327</v>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>○ 原資料と一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>減価償却費（財政シミュ Row52）</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>395267</v>
+      </c>
+      <c r="C7" s="17" t="n">
+        <v>414923</v>
+      </c>
+      <c r="D7" s="17" t="n">
+        <v>412864</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>407154</v>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>402234</v>
+      </c>
+      <c r="G7" s="17" t="n">
+        <v>2032442</v>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>○ 一致（原資料2,032,440。丸め差2千円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>支払利息 既往債（同 Row60）</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>10790</v>
+      </c>
+      <c r="C8" s="16" t="n">
+        <v>10530</v>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>10172</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>9805</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>9288</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>50585</v>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>○ 一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>支払利息 新規債（同 Row61）</t>
+        </is>
+      </c>
+      <c r="B9" s="17" t="n">
+        <v>9238</v>
+      </c>
+      <c r="C9" s="17" t="n">
+        <v>18507</v>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>26641</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>34316</v>
+      </c>
+      <c r="F9" s="17" t="n">
+        <v>38700</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>127402</v>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>○ 一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>★長期前受金戻入益（同 Row16）</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="n">
+        <v>-329946</v>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>-324870</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>-311865</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>-299986</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>-290154</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>-1556820</v>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>× 原資料は▲450,000千円（3.46倍の差）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>★ 原資料の備考には「（推計値）財政シミュR6〜R7平均から推計。要精査。」と明記されています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 ただし財政シミュのR6は334,202千円、R7は334,252千円で、その平均から5年分を推計しても約1,671,000千円となり、450,000千円にはなりません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>★ 他の4費目はすべて財政シミュの値と一致しています。長期前受金戻入益だけが置き換えられないまま残ったプレースホルダと判断されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>★ 正しい控除額は、財政シミュの令和８〜12年度の予測値の合計 ▲1,556,820千円です（逓減を織り込んだ値）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>■　(2) 総括原価の再計算（資産維持率別・5年計・千円）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>資産維持率</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>資産維持費
+5年計</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>総括原価
+5年計</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>給水原価
+（案の有収水量）</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>給水原価
+（見直し後）</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>必要改定率
+（案）</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>必要改定率
+（見直し後）</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
         <is>
           <t>備　考</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>維持管理費</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
-        <v>672327</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>672327</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>年平均134,465千円。令和７年度の平常時（江島分控除後）137,751千円とほぼ一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>減価償却費</t>
-        </is>
-      </c>
-      <c r="B14" s="17" t="n">
-        <v>2032440</v>
-      </c>
-      <c r="C14" s="17" t="n">
-        <v>2032440</v>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="15" t="inlineStr">
-        <is>
-          <t>年平均406,488千円。令和７年度実績393,746千円</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>既往債利息</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>50585</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>50585</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>年平均10,117千円</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>新規債利息</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="n">
-        <v>127402</v>
-      </c>
-      <c r="C16" s="17" t="n">
-        <v>127402</v>
-      </c>
-      <c r="D16" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="15" t="inlineStr">
-        <is>
-          <t>年平均25,480千円。★令和７年度の新規借入利率は加重平均2.58％</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>資産維持費（3％）</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>134445</v>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>134445</v>
-      </c>
-      <c r="D17" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>対象資産896,300千円×3％×5年。★対象資産の範囲の根拠確認が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>小　計</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n">
-        <v>3017199</v>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>3017199</v>
-      </c>
-      <c r="D18" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="15" t="inlineStr"/>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>控除　長期前受金戻入益</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="n">
-        <v>-450000</v>
-      </c>
-      <c r="C19" s="20" t="n">
-        <v>-1671262</v>
-      </c>
-      <c r="D19" s="20" t="n">
-        <v>-1221262</v>
-      </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>★令和７年度実績334,252千円×5年</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>1.0％　試算シートの現設定</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>44816</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>1355752</v>
+      </c>
+      <c r="D19" s="34" t="n">
+        <v>314.1</v>
+      </c>
+      <c r="E19" s="34" t="n">
+        <v>281.7</v>
+      </c>
+      <c r="F19" s="26" t="inlineStr">
+        <is>
+          <t>＋169.4％</t>
+        </is>
+      </c>
+      <c r="G19" s="26" t="inlineStr">
+        <is>
+          <t>＋141.6％</t>
+        </is>
+      </c>
+      <c r="H19" s="13" t="inlineStr"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>控除　他会計補助金等</t>
+          <t>1.5％　原資料の推奨下限</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>-15000</v>
+        <v>67223</v>
       </c>
       <c r="C20" s="17" t="n">
-        <v>-15000</v>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="15" t="inlineStr"/>
-    </row>
-    <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
-        <is>
-          <t>★総括原価</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="n">
-        <v>2552199</v>
-      </c>
-      <c r="C21" s="31" t="n">
-        <v>1330937</v>
-      </c>
-      <c r="D21" s="31" t="n">
-        <v>-1221262</v>
-      </c>
-      <c r="E21" s="21" t="inlineStr"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>■　給水原価（総括原価ベース）と必要改定率</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>前　提</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>総括原価
-5年計（千円）</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>有収水量
-5年計（千㎥）</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>給水原価
-（円/㎥）</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>料金回収率100％に必要な改定率</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>引継ぎメモのまま</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="n">
-        <v>2552199</v>
-      </c>
-      <c r="C25" s="20" t="n">
-        <v>4307</v>
-      </c>
-      <c r="D25" s="34" t="n">
-        <v>592.5</v>
-      </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>＋327.2％</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>控除額のみ是正（有収水量は案のまま）</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="n">
-        <v>1330937</v>
-      </c>
-      <c r="C26" s="18" t="n">
-        <v>4307</v>
-      </c>
-      <c r="D26" s="35" t="n">
-        <v>309</v>
-      </c>
-      <c r="E26" s="27" t="inlineStr">
-        <is>
-          <t>＋122.8％</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
-        <is>
-          <t>★控除額の是正＋有収水量の見直し</t>
-        </is>
-      </c>
-      <c r="B27" s="31" t="n">
-        <v>1330937</v>
-      </c>
-      <c r="C27" s="31" t="n">
-        <v>4802</v>
-      </c>
-      <c r="D27" s="36" t="n">
-        <v>277.2</v>
-      </c>
-      <c r="E27" s="22" t="inlineStr">
-        <is>
-          <t>＋122.8％</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="15" t="inlineStr">
-        <is>
-          <t>（参考）資産維持費を算入しない場合</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="n">
-        <v>1196492</v>
-      </c>
-      <c r="C28" s="17" t="n">
-        <v>4802</v>
-      </c>
-      <c r="D28" s="37" t="n">
-        <v>249.2</v>
-      </c>
-      <c r="E28" s="25" t="inlineStr">
-        <is>
-          <t>＋100.3％</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>※ 有収水量5年計は、経営戦略（案）の令和８年度901千㎥・令和17年度723千㎥を線形補間して令和８〜12年度分を積み上げたものです（4,307千㎥）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　 引継ぎメモの給水原価572円は約4,462千㎥を前提とした値と推定され、当方の補間値との差（約4％）が592.5円との差になっています。原価側の差ではありません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>※ 必要改定率は「総括原価の年平均 ÷ 令和７年度の給水収益119,480,750円」で算定しています（有収水量の増減は考慮していない簡易計算）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>★ 引継ぎメモの給水原価572円に対し、控除額を実績ベースに是正すると300円前後まで下がります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　 「1回の改定では不十分」という結論自体は変わりませんが、住民・議会に示す数値としては大きな差です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>★ 本シートは引継ぎメモ記載の費目を前提とした再計算です。原資料（onagawa_cost_sim_v1.xlsx、onagawa_tariff_cost_calc.xlsx）での確認が必要です。</t>
+        <v>1378159</v>
+      </c>
+      <c r="D20" s="35" t="n">
+        <v>319.3</v>
+      </c>
+      <c r="E20" s="35" t="n">
+        <v>286.4</v>
+      </c>
+      <c r="F20" s="25" t="inlineStr">
+        <is>
+          <t>＋173.8％</t>
+        </is>
+      </c>
+      <c r="G20" s="25" t="inlineStr">
+        <is>
+          <t>＋145.6％</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>2.0％　原資料の推奨</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>89631</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>1400567</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <v>324.5</v>
+      </c>
+      <c r="E21" s="34" t="n">
+        <v>291.1</v>
+      </c>
+      <c r="F21" s="26" t="inlineStr">
+        <is>
+          <t>＋178.3％</t>
+        </is>
+      </c>
+      <c r="G21" s="26" t="inlineStr">
+        <is>
+          <t>＋149.6％</t>
+        </is>
+      </c>
+      <c r="H21" s="13" t="inlineStr"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>2.3％　松山市事例</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>103076</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>1414012</v>
+      </c>
+      <c r="D22" s="35" t="n">
+        <v>327.6</v>
+      </c>
+      <c r="E22" s="35" t="n">
+        <v>293.9</v>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>＋181.0％</t>
+        </is>
+      </c>
+      <c r="G22" s="25" t="inlineStr">
+        <is>
+          <t>＋152.0％</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr"/>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="21" t="inlineStr">
+        <is>
+          <t>3.0％　要領標準／引継ぎメモの正式ケース</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="n">
+        <v>134447</v>
+      </c>
+      <c r="C23" s="31" t="n">
+        <v>1445383</v>
+      </c>
+      <c r="D23" s="36" t="n">
+        <v>334.9</v>
+      </c>
+      <c r="E23" s="36" t="n">
+        <v>300.4</v>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>＋187.2％</t>
+        </is>
+      </c>
+      <c r="G23" s="22" t="inlineStr">
+        <is>
+          <t>＋157.6％</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>★引継ぎメモは3％を正式ケースとするが、原資料は1.5〜2.0％を推奨。要統一</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>※ 基礎費用（維持管理費＋減価償却費＋既往債利息＋新規債利息）2,882,756千円、控除（長期前受金戻入益▲1,556,820＋他会計補助金等▲15,000）▲1,571,820千円。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>※ 資産維持費 ＝ 対象資産（期首期末平均896,313千円）× 資産維持率 × 5年。日本水道協会「水道料金算定要領」は期首期末平均を用いる。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>※ 有収水量は、案の推計4,316千㎥（R8:901→R12:818）と、見直し後4,812千㎥（直近3か年平均489L基準・＋11.5％）の2通り。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>★ 必要改定率 ＝ 給水原価 ÷ 現行供給単価116.61円（税抜）− 1。分子と分母を同じ有収水量ベースで揃えています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>■　(3) 他の算定基準との整合</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>基　準</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>給水原価（円/㎥）</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>必要改定率</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>位置づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>令和７年度 平常時ベース（一過性を除く）</t>
+        </is>
+      </c>
+      <c r="B32" s="37" t="n">
+        <v>206.8</v>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>＋77.3％</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>現状維持の下限</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>★総括原価ベース（3％・有収水量見直し後）</t>
+        </is>
+      </c>
+      <c r="B33" s="38" t="n">
+        <v>300.4</v>
+      </c>
+      <c r="C33" s="22" t="inlineStr">
+        <is>
+          <t>＋157.6％</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>将来の投資と更新財源を織り込んだ水準</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>令和７年度 経営比較分析表ベース</t>
+        </is>
+      </c>
+      <c r="B34" s="37" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>＋185.1％</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>江島の一過性費用を料金で回収する場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>総括原価ベース（3％・案の有収水量）</t>
+        </is>
+      </c>
+      <c r="B35" s="39" t="n">
+        <v>334.9</v>
+      </c>
+      <c r="C35" s="27" t="inlineStr">
+        <is>
+          <t>＋187.2％</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>有収水量を見直さない場合</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>※ 総括原価ベース（見直し後）300.4円は、令和７年度の経営比較分析表ベース332.50円と平常時ベース206.80円の間に位置し、整合的です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 将来は減価償却費と新規債利息が増える一方、江島海底送水管の応急給水費用がなくなるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>【訂正】当方が令和８年８月３日にお伝えした必要改定率＋122.8％は誤りでした。総括原価の年平均を令和７年度の給水収益で除していましたが、</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　　　両者は有収水量の前提が異なります。分子と分母を同じ有収水量ベースで揃えると、上表のとおり＋141.6〜187.2％となります。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A30:E30"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="A4:E4"/>
+  <mergeCells count="17">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>５　原資料の要修正箇所</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>onagawa_tariff_cost_calc.xlsx ／ onagawa_cost_sim_v1.xlsx の確認結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>箇　所</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>現　状</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>修正の内容</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>優先度</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="62" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>控除：長期前受金戻入益</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>▲450,000千円（5年計）。備考「（推計値）財政シミュR6〜R7平均から推計。要精査。」</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>★財政シミュ Row16 の令和８〜12年度の値 ▲1,556,820千円に差替。総括原価が約111万千円増える</t>
+        </is>
+      </c>
+      <c r="E5" s="40" t="inlineStr">
+        <is>
+          <t>★最優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>cost_sim_v1「総括原価シミュレーション」【A】合計行</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>R9以降が累計値（R8:459,184／R9:950,289／R10:1,450,381／R11:1,955,360／R12:2,462,569）。5年合計は7,277,783千円</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>★年度別の値に修正（R9:491,105／R10:500,092／R11:504,979／R12:507,209）。正しい5年合計は2,462,569千円</t>
+        </is>
+      </c>
+      <c r="E6" s="40" t="inlineStr">
+        <is>
+          <t>★最優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="62" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>同【B】給水原価・料金回収率</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>給水原価1,686.2円、料金回収率8％。誤った5年合計7,277,783千円を用いているため</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>No.2の修正により給水原価570.6円・料金回収率22％となる（現設定1.0％の場合）。【C】感度分析は正しく計算されている</t>
+        </is>
+      </c>
+      <c r="E7" s="40" t="inlineStr">
+        <is>
+          <t>★最優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="62" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>tariff_cost_calc【C】給水原価（算定）</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>「約0円/㎥」と表示。計算されていない</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t>2,469,884千円 ÷ 4,316千㎥ ＝ 572.3円（現行の控除額のまま）。No.1修正後は約300〜335円</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>資産維持率の設定</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>試算シート1.0％／tariff_cost_calc推奨1.5〜2.0％／cost_sim_v1入力1.0％（推奨2.0％）／引継ぎメモ「3％（正式ケース）」の4通り</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>★どれを正式とするか決定。要領標準は3％だが、原資料は「改定率が大きくなりすぎない範囲」として1.5〜2.0％を推奨している</t>
+        </is>
+      </c>
+      <c r="E9" s="40" t="inlineStr">
+        <is>
+          <t>★最優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>資産維持費の対象資産の時点</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>1,042,625,176円は試算シート記載のH31（令和元年度）末帳簿価額（原浄水281,981千円＋配給水760,644千円）</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>★7年前の値。令和７年度決算で固定資産の計上誤りが大幅に修正されているため、R7末の固定資産台帳で再集計が必要</t>
+        </is>
+      </c>
+      <c r="E10" s="40" t="inlineStr">
+        <is>
+          <t>★最優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="62" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>資産維持費の対象資産の取り方</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>tariff_cost_calc は期首1,042,625千円で算定（年10,426千円）、cost_sim_v1 は期首期末平均896,313千円で算定（年8,963千円）</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>要領は期首期末平均。cost_sim_v1 の方式に統一</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="62" customHeight="1">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>料金算定期間</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>試算シート【料金算定】資産維持費は4年、tariff_cost_calc／cost_sim_v1 は5年（R8〜R12）</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>5年に統一するか要確認。資産維持費の総額が変わる</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="62" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>現行の供給単価・給水原価・料金回収率</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>128.2円（税込）／242円（R5回収率からの逆算）／52.87％（R5の値）</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>★116.61円（税抜）／332.50円（R7経営比較分析表）／35.07％（R7）に差替。シート02の使い分け表に従う</t>
+        </is>
+      </c>
+      <c r="E13" s="40" t="inlineStr">
+        <is>
+          <t>★最優先</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="62" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>有収水量</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>4,316千㎥（R8:901→R12:818）。経営戦略（案）の推計をそのまま使用</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>令和７年度実績1,024,576㎥を12％下回る。シート03の見直し案の適用を検討</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>※ No.2・3は数式の不具合です。cost_sim_v1 の【C】感度分析は正しく計算されているため、こちらの値（1.0％で総括原価2,462,569千円・給水原価570.6円）が正です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>※ 感度分析の給水原価570.6〜591.3円も、No.1（長期前受金戻入益）の修正により約300〜335円に下がります。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A16:E16"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A17:E17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/onagawa/output/女川町_水道_数値定義と確定値一覧.xlsx
+++ b/onagawa/output/女川町_水道_数値定義と確定値一覧.xlsx
@@ -11,8 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_確定値一覧_R7決算" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_指標の算式と値" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_有収水量推計の見直し" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_総括原価の検証と再計算" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_原資料の要修正箇所" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_対象資産の算定" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_総括原価の検証と再計算" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_原資料の要修正箇所" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -142,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -228,30 +229,45 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -259,6 +275,9 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2030,21 +2049,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>３　有収水量推計の見直し</t>
+          <t>３　有収水量推計の見直し　－　見直し案Ａを採用</t>
         </is>
       </c>
     </row>
@@ -2169,12 +2188,12 @@
       <c r="B9" s="22" t="inlineStr"/>
       <c r="C9" s="22" t="inlineStr"/>
       <c r="D9" s="32" t="n">
-        <v>489.3</v>
+        <v>489.26</v>
       </c>
       <c r="E9" s="23" t="inlineStr"/>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>★見直し推計の基礎とする</t>
+          <t>★見直し推計の基礎に採用</t>
         </is>
       </c>
     </row>
@@ -2205,343 +2224,916 @@
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>■　見直し案</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>■【採用】見直し案Ａ　＝　給水人口 × 489.26L　（料金算定対象期間 R8〜R12）</t>
         </is>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>推計方法</t>
+          <t>年　度</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>令和８年度（㎥）</t>
+          <t>給水人口（人）</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>令和17年度（㎥）</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>案との差</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>評　価</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>経営戦略（案）＝給水人口 × 439L</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="n">
-        <v>901000</v>
-      </c>
-      <c r="C14" s="20" t="n">
-        <v>723000</v>
-      </c>
-      <c r="D14" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>★令和７年度実績1,024,576㎥を12％下回る。初年度から実績と乖離する推計</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
-        <is>
-          <t>見直し案Ａ＝給水人口 × 489L（直近3か年平均）</t>
-        </is>
-      </c>
-      <c r="B15" s="31" t="n">
+          <t>有収水量（㎥）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>令和8年度</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>5625</v>
+      </c>
+      <c r="C14" s="16" t="n">
         <v>1004512</v>
       </c>
-      <c r="C15" s="31" t="n">
-        <v>805395</v>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>＋11.5％</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>実績の水準を反映。最も簡便で説明しやすい</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>見直し案Ｂ＝用途別（家事用は人口比例、非家事用は別トレンド）</t>
-        </is>
-      </c>
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>要試算</t>
-        </is>
-      </c>
-      <c r="C16" s="27" t="inlineStr">
-        <is>
-          <t>要試算</t>
-        </is>
-      </c>
-      <c r="D16" s="27" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>★理論的には最も妥当。ただし非家事用のトレンド設定に事業所側の情報が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>■【重要】用途区分別の有収水量シェア　－　給水人口比例の推計が成り立つのは44.5％だけ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>用途区分</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>水量（㎥／月）</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>シェア（％）</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>備　考</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>家事用</t>
-        </is>
-      </c>
-      <c r="B20" s="31" t="n">
-        <v>2471</v>
-      </c>
-      <c r="C20" s="31" t="n">
-        <v>34668</v>
-      </c>
-      <c r="D20" s="32" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="E20" s="21" t="inlineStr"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>工業用</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="n">
-        <v>66</v>
-      </c>
-      <c r="C21" s="20" t="n">
-        <v>28067</v>
-      </c>
-      <c r="D21" s="33" t="n">
-        <v>36.1</v>
-      </c>
-      <c r="E21" s="9" t="inlineStr"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>団体用</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n">
-        <v>195</v>
-      </c>
-      <c r="C22" s="16" t="n">
-        <v>7498</v>
-      </c>
-      <c r="D22" s="29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="E22" s="13" t="inlineStr"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>営業用</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n">
-        <v>298</v>
-      </c>
-      <c r="C23" s="17" t="n">
-        <v>6908</v>
-      </c>
-      <c r="D23" s="30" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="E23" s="15" t="inlineStr"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>湯屋用</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C24" s="16" t="n">
-        <v>662</v>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E24" s="13" t="inlineStr"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>臨時用</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n">
-        <v>26</v>
-      </c>
-      <c r="C25" s="17" t="n">
-        <v>33</v>
-      </c>
-      <c r="D25" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="15" t="inlineStr"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>委託船舶給水用</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="D26" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="13" t="inlineStr"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>合　計</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="n">
-        <v>3059</v>
-      </c>
-      <c r="C27" s="17" t="n">
-        <v>77847</v>
-      </c>
-      <c r="D27" s="30" t="n">
-        <v>100</v>
-      </c>
-      <c r="E27" s="15" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>令和9年度</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>5501</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>982388</v>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>令和10年度</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n">
+        <v>5377</v>
+      </c>
+      <c r="C16" s="16" t="n">
+        <v>960264</v>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>令和11年度</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>5253</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>938140</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>令和12年度</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>5129</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>916016</v>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>5年計</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr"/>
+      <c r="C19" s="31" t="n">
+        <v>4801318</v>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>（参考）経営戦略（案）5年計</t>
+        </is>
+      </c>
+      <c r="B20" s="28" t="inlineStr"/>
+      <c r="C20" s="20" t="n">
+        <v>4316000</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>※ 5年計 4,801,318㎥。経営戦略（案）の4,316,000㎥に対し ＋11.2％。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>【なぜ見直し案Ａを採用したか】</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>① 経営戦略（案）の439.0L／人日は過去10年平均で、震災復興期（有収水量が低く、復興作業員により給水人口が多かった時期）を含みます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 直近3か年の実績は484.0〜496.3Lで、案の前提を10％以上上回っています。令和８年度の推計901千㎥は令和７年度実績1,024,576㎥を12％下回り、初年度から実績と乖離します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>② 有収水量の実績はR2〜R7の6年間で1,020〜1,053千㎥とほぼ横ばいです（年▲0.1％程度）。案の「R6の1,019千㎥からR8に901千㎥へ11.6％減」という想定は、実績の推移と整合しません。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>③ 総務省マニュアルの標準的手法（給水人口 × 1人1日あたり有収水量）の枠組みを維持し、基礎数値だけを直近実績に差し替える方式のため、</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>※ 調定データ（1か月分3,060件）より集計。</t>
+          <t xml:space="preserve">　 経営戦略（案）本文の修正が最小で済み、令和８年９月末の中間報告に間に合います。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>★ 家事用は有収水量の44.5％にすぎず、工業用が36.1％（66件）を占めます。工業用の大半は水産加工業です。</t>
-        </is>
-      </c>
+      <c r="A30" s="4" t="inlineStr"/>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>★ 経営戦略（案）は有収水量の全量を「給水人口 × 1人1日あたり有収水量」で推計していますが、</t>
+          <t>【採用しなかった案と、その理由】</t>
         </is>
       </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 55.5％を占める非家事用は給水人口に連動しません。推計方法そのものに構造的な弱点があります。</t>
+          <t>・用途別推計（家事用は給水人口比例、非家事用は別トレンド）… 理論的には最も妥当ですが、非家事用（有収水量の55.5％）のトレンド設定に</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>※ 見直し案Ｂを採る場合、水産加工業の生産動向・事業所数の見通しについて町・事業者への確認が必要です。</t>
+          <t xml:space="preserve">　 水産加工業の生産動向・事業所数の見通しが必要で、中間報告までに確定できません。次期の経営戦略改定時に移行することを推奨します。</t>
         </is>
       </c>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>※ なお、給水人口の推計値（令和８年度5,625人）は令和７年度実績5,656人と整合しており、こちらは差し替え不要です。</t>
+      <c r="A34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>【案Ａの限界（本文に注記すべき事項）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>・案Ａは有収水量の全量に給水人口の減少率を適用します。実際には非家事用（55.5％）は給水人口に連動しないため、</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 非家事用が横ばいで推移する場合には過小推計となります。この意味で案Ａは保守的（原価を高めに、改定率を高めに見積もる）側の推計です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>■　用途区分別の有収水量シェア　－　給水人口比例が成り立つのは44.5％だけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>用途区分</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>水量（㎥／月）</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>シェア（％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>家事用</t>
+        </is>
+      </c>
+      <c r="B41" s="31" t="n">
+        <v>2471</v>
+      </c>
+      <c r="C41" s="31" t="n">
+        <v>34668</v>
+      </c>
+      <c r="D41" s="34" t="n">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>工業用</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="C42" s="20" t="n">
+        <v>28067</v>
+      </c>
+      <c r="D42" s="35" t="n">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>団体用</t>
+        </is>
+      </c>
+      <c r="B43" s="16" t="n">
+        <v>195</v>
+      </c>
+      <c r="C43" s="16" t="n">
+        <v>7498</v>
+      </c>
+      <c r="D43" s="36" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>営業用</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>298</v>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>6908</v>
+      </c>
+      <c r="D44" s="37" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>湯屋用</t>
+        </is>
+      </c>
+      <c r="B45" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="16" t="n">
+        <v>662</v>
+      </c>
+      <c r="D45" s="36" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="15" t="inlineStr">
+        <is>
+          <t>臨時用</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D46" s="37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>委託船舶給水用</t>
+        </is>
+      </c>
+      <c r="B47" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="D47" s="36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="15" t="inlineStr">
+        <is>
+          <t>合　計</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>3059</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>77847</v>
+      </c>
+      <c r="D48" s="37" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>※ 調定データ（1か月分3,060件）より集計。家事用は44.5％にすぎず、工業用が36.1％をわずか66件（大半が水産加工業）で占めています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>※ なお給水人口の推計値（令和８年度5,625人）は令和７年度実績5,656人と整合しており、差し替えは不要です。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="23">
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A28:F28"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="002E75B6"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>４　資産維持費の対象資産の算定　－　料金算定対象期間（R8〜R12）の平均</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>出典：令和７年度 有形固定資産明細書・貸借対照表／経営戦略試算シート【成行】財政シミュ 資本的収支</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>■　(1) 起点となる令和７年度末の実績</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>区　分</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>金額（円）</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>備　考</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>有形固定資産（帳簿価額）</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>9159891337</v>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>貸借対照表・有形固定資産明細書</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　△ 土地</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n">
+        <v>-46918915</v>
+      </c>
+      <c r="C7" s="15" t="inlineStr">
+        <is>
+          <t>償却資産ではないため除外</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　△ 建設仮勘定</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>-29400000</v>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>★償却資産の帳簿価額</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="n">
+        <v>9083572422</v>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>建物680,390,033＋構築物6,780,666,481＋機械装置1,612,678,880＋工具器具46,200＋量水器9,790,828</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　△ 長期前受金（未収益化残高）</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>-7491683492</v>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>補助金等で取得した資産に見合う部分</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>★対象資産（定義Ｂ・採用）</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n">
+        <v>1591888930</v>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>自己財源（企業債・出資金・自己資金）見合いの償却資産</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>★ 従前の試算で用いていた対象資産1,042,625,176円は、試算シート記載のH31（令和元年度）末帳簿価額（取水124,491,503＋浄水157,489,766＋配水760,643,907）でした。</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 令和７年度の実績（浄水1,333,550,491／配水給水5,164,069,770 ほか）と大きく異なり、当時の固定資産台帳が不完全であったことが確認できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 令和７年度決算で減価償却累計額等が大幅に修正されているため、令和７年度末の明細書を起点としました。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>■　(2) 料金算定対象期間の推移</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>年　度</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>定義Ａ 償却資産</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>長期前受金残高</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>★定義Ｂ 対象資産</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>当年度取得（税抜）</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>当年度減価償却費</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>令和７年度末（期首）</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n">
+        <v>9083572422</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>7491683492</v>
+      </c>
+      <c r="D19" s="16" t="n">
+        <v>1591888930</v>
+      </c>
+      <c r="E19" s="26" t="inlineStr"/>
+      <c r="F19" s="26" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>令和８年度末</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>9624668749</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>7228067464</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>2396601285</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>936363636</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>395267309</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>令和９年度末</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>10073382025</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>6956197363</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>3117184662</v>
+      </c>
+      <c r="E21" s="16" t="n">
+        <v>863636364</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>414923088</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>令和10年度末</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>10115063910</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>6697332623</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>3417731287</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>454545455</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>412863570</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>令和11年度末</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="n">
+        <v>10007910044</v>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>6450347090</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>3557562954</v>
+      </c>
+      <c r="E23" s="16" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="F23" s="16" t="n">
+        <v>407153866</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>令和12年度末</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>9887493862</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>6213193354</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>3674300508</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>281818182</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>402234363</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>★期首期末平均</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="n">
+        <v>9485533142</v>
+      </c>
+      <c r="C25" s="31" t="n">
+        <v>6852438423</v>
+      </c>
+      <c r="D25" s="31" t="n">
+        <v>2633094719</v>
+      </c>
+      <c r="E25" s="22" t="inlineStr"/>
+      <c r="F25" s="22" t="inlineStr"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>（参考）各年度平均</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>9798681835</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>6839470231</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>2959211604</v>
+      </c>
+      <c r="E26" s="25" t="inlineStr"/>
+      <c r="F26" s="25" t="inlineStr"/>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>※ 取得額は財政シミュの建設改良費（税込）を1.1で除した税抜相当額。長期前受金の増加は国庫補助金＋他会計補助金（出資金は資本金であり長期前受金にならない）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>※ 定義Ｂが期間中に1,592百万円→3,674百万円と増えるのは、令和８年度以降の投資（5年計 税抜2,836百万円）の財源が</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 企業債1,712百万円＋出資金1,130百万円で、補助金は275百万円にとどまるためです。復興期（補助金中心）からの構造変化が表れています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>★ 料金算定対象期間の平均は、日本水道協会「水道料金算定要領」に従い期首期末平均を採用しました（各年度平均も併記）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>■　(3) 対象資産の定義について</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="28" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>定　義</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>期首期末平均</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>3％の場合の年額</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>給水収益に対する比</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t>評　価</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="46" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>定義Ａ　償却資産の帳簿価額（要領の文言どおり）</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="n">
+        <v>9485533142</v>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>284565994</v>
+      </c>
+      <c r="D35" s="28" t="inlineStr">
+        <is>
+          <t>238％</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>★女川町は資産の82％が補助金等で取得されているため、この定義では資産維持費が給水収益の2.4倍となり実務的でない</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="46" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>★定義Ｂ　償却資産 − 長期前受金（採用）</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="n">
+        <v>2633094719</v>
+      </c>
+      <c r="C36" s="31" t="n">
+        <v>78992842</v>
+      </c>
+      <c r="D36" s="22" t="inlineStr">
+        <is>
+          <t>66％</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
+        <is>
+          <t>総括原価で長期前受金戻入益を控除していることと整合する。自己財源で更新すべき資産に対応</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A28:G28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -2558,13 +3150,13 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="54" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>４　総括原価の検証と再計算</t>
+          <t>５　総括原価の検証と再計算</t>
         </is>
       </c>
     </row>
@@ -2795,412 +3387,382 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>★ 正しい控除額は、財政シミュの令和８〜12年度の予測値の合計 ▲1,556,820千円です（逓減を織り込んだ値）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>■　(2) 総括原価の再計算（資産維持率別・5年計・千円）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>■　(2) 総括原価と必要改定率（資産維持率 1％・2％・3％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>資産維持率</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>対象資産
+（期首期末平均・千円）</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>資産維持費
-5年計</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
+5年計（千円）</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>総括原価
-5年計</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
+5年計（千円）</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>給水原価
-（案の有収水量）</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>給水原価
-（見直し後）</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>必要改定率
-（案）</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>必要改定率
-（見直し後）</t>
-        </is>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>備　考</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>1.0％　試算シートの現設定</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>44816</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>1355752</v>
-      </c>
-      <c r="D19" s="34" t="n">
-        <v>314.1</v>
-      </c>
-      <c r="E19" s="34" t="n">
-        <v>281.7</v>
-      </c>
-      <c r="F19" s="26" t="inlineStr">
-        <is>
-          <t>＋169.4％</t>
-        </is>
-      </c>
-      <c r="G19" s="26" t="inlineStr">
-        <is>
-          <t>＋141.6％</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr"/>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>1.5％　原資料の推奨下限</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n">
-        <v>67223</v>
-      </c>
-      <c r="C20" s="17" t="n">
-        <v>1378159</v>
-      </c>
-      <c r="D20" s="35" t="n">
-        <v>319.3</v>
-      </c>
-      <c r="E20" s="35" t="n">
-        <v>286.4</v>
-      </c>
-      <c r="F20" s="25" t="inlineStr">
-        <is>
-          <t>＋173.8％</t>
-        </is>
-      </c>
-      <c r="G20" s="25" t="inlineStr">
-        <is>
-          <t>＋145.6％</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="inlineStr"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>2.0％　原資料の推奨</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>89631</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>1400567</v>
-      </c>
-      <c r="D21" s="34" t="n">
-        <v>324.5</v>
-      </c>
-      <c r="E21" s="34" t="n">
-        <v>291.1</v>
-      </c>
-      <c r="F21" s="26" t="inlineStr">
-        <is>
-          <t>＋178.3％</t>
-        </is>
-      </c>
-      <c r="G21" s="26" t="inlineStr">
-        <is>
-          <t>＋149.6％</t>
-        </is>
-      </c>
-      <c r="H21" s="13" t="inlineStr"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>2.3％　松山市事例</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n">
-        <v>103076</v>
-      </c>
-      <c r="C22" s="17" t="n">
-        <v>1414012</v>
-      </c>
-      <c r="D22" s="35" t="n">
-        <v>327.6</v>
-      </c>
-      <c r="E22" s="35" t="n">
-        <v>293.9</v>
-      </c>
-      <c r="F22" s="25" t="inlineStr">
-        <is>
-          <t>＋181.0％</t>
-        </is>
-      </c>
-      <c r="G22" s="25" t="inlineStr">
-        <is>
-          <t>＋152.0％</t>
-        </is>
-      </c>
-      <c r="H22" s="15" t="inlineStr"/>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="21" t="inlineStr">
-        <is>
-          <t>3.0％　要領標準／引継ぎメモの正式ケース</t>
-        </is>
-      </c>
-      <c r="B23" s="31" t="n">
-        <v>134447</v>
-      </c>
-      <c r="C23" s="31" t="n">
-        <v>1445383</v>
-      </c>
-      <c r="D23" s="36" t="n">
-        <v>334.9</v>
-      </c>
-      <c r="E23" s="36" t="n">
-        <v>300.4</v>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
-        <is>
-          <t>＋187.2％</t>
-        </is>
-      </c>
-      <c r="G23" s="22" t="inlineStr">
+（円/㎥）</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>必要改定率</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>現行の料金回収率
+（％）</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>20㎥家庭料金
+（改定後・税込）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>1％</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="n">
+        <v>2633095</v>
+      </c>
+      <c r="C18" s="31" t="n">
+        <v>131655</v>
+      </c>
+      <c r="D18" s="31" t="n">
+        <v>1442591</v>
+      </c>
+      <c r="E18" s="38" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>＋157.6％</t>
         </is>
       </c>
-      <c r="H23" s="24" t="inlineStr">
-        <is>
-          <t>★引継ぎメモは3％を正式ケースとするが、原資料は1.5〜2.0％を推奨。要統一</t>
+      <c r="G18" s="34" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>6,377円</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>2％</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n">
+        <v>2633095</v>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>263309</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <v>1574245</v>
+      </c>
+      <c r="E19" s="39" t="n">
+        <v>327.9</v>
+      </c>
+      <c r="F19" s="27" t="inlineStr">
+        <is>
+          <t>＋181.2％</t>
+        </is>
+      </c>
+      <c r="G19" s="40" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="H19" s="27" t="inlineStr">
+        <is>
+          <t>6,959円</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>3％</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n">
+        <v>2633095</v>
+      </c>
+      <c r="C20" s="20" t="n">
+        <v>394964</v>
+      </c>
+      <c r="D20" s="20" t="n">
+        <v>1705900</v>
+      </c>
+      <c r="E20" s="41" t="n">
+        <v>355.3</v>
+      </c>
+      <c r="F20" s="28" t="inlineStr">
+        <is>
+          <t>＋204.7％</t>
+        </is>
+      </c>
+      <c r="G20" s="35" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="H20" s="28" t="inlineStr">
+        <is>
+          <t>7,541円</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>※ 基礎費用（維持管理費＋減価償却費＋既往債利息＋新規債利息）2,882,756千円、控除（長期前受金戻入益▲1,556,820＋他会計補助金等▲15,000）-1,571,820千円。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>※ 有収水量は見直し案Ａの5年計 4,801,318㎥（シート03）。対象資産は定義Ｂの期首期末平均 2,633,094,719円（シート04）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>★ 必要改定率 ＝ 給水原価 ÷ 現行供給単価116.61円（税抜）− 1。分子と分母を同じ有収水量ベースで揃えています。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>※ 基礎費用（維持管理費＋減価償却費＋既往債利息＋新規債利息）2,882,756千円、控除（長期前受金戻入益▲1,556,820＋他会計補助金等▲15,000）▲1,571,820千円。</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>※ 資産維持費 ＝ 対象資産（期首期末平均896,313千円）× 資産維持率 × 5年。日本水道協会「水道料金算定要領」は期首期末平均を用いる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>※ 有収水量は、案の推計4,316千㎥（R8:901→R12:818）と、見直し後4,812千㎥（直近3か年平均489L基準・＋11.5％）の2通り。</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>★ 必要改定率 ＝ 給水原価 ÷ 現行供給単価116.61円（税抜）− 1。分子と分母を同じ有収水量ベースで揃えています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>■　(3) 他の算定基準との整合</t>
+          <t>★ 20㎥家庭料金は現行2,475円（税込・メーター使用料を含む）に必要改定率を一律に乗じた参考値です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>■　(3) 他の算定基準との整合と、実務上の含意</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>基　準</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>給水原価（円/㎥）</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>必要改定率</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>位置づけ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>令和７年度 平常時ベース（一過性を除く）</t>
+        </is>
+      </c>
+      <c r="B29" s="42" t="n">
+        <v>206.8</v>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>＋77.3％</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>現状維持の下限。将来の投資を含まない</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>★総括原価ベース（資産維持率1％）</t>
+        </is>
+      </c>
+      <c r="B30" s="43" t="n">
+        <v>300.5</v>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>＋157.6％</t>
+        </is>
+      </c>
+      <c r="D30" s="21" t="inlineStr">
+        <is>
+          <t>将来の投資を織り込んだ最小水準</t>
         </is>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>基　準</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>給水原価（円/㎥）</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>必要改定率</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr">
-        <is>
-          <t>位置づけ</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>令和７年度 平常時ベース（一過性を除く）</t>
-        </is>
-      </c>
-      <c r="B32" s="37" t="n">
-        <v>206.8</v>
-      </c>
-      <c r="C32" s="26" t="inlineStr">
-        <is>
-          <t>＋77.3％</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>現状維持の下限</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
-        <is>
-          <t>★総括原価ベース（3％・有収水量見直し後）</t>
-        </is>
-      </c>
-      <c r="B33" s="38" t="n">
-        <v>300.4</v>
-      </c>
-      <c r="C33" s="22" t="inlineStr">
-        <is>
-          <t>＋157.6％</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>将来の投資と更新財源を織り込んだ水準</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>令和７年度 経営比較分析表ベース</t>
         </is>
       </c>
-      <c r="B34" s="37" t="n">
+      <c r="B31" s="42" t="n">
         <v>332.5</v>
       </c>
-      <c r="C34" s="26" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>＋185.1％</t>
         </is>
       </c>
-      <c r="D34" s="13" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>江島の一過性費用を料金で回収する場合</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>総括原価ベース（3％・案の有収水量）</t>
-        </is>
-      </c>
-      <c r="B35" s="39" t="n">
-        <v>334.9</v>
-      </c>
-      <c r="C35" s="27" t="inlineStr">
-        <is>
-          <t>＋187.2％</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>有収水量を見直さない場合</t>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>総括原価ベース（資産維持率2％）</t>
+        </is>
+      </c>
+      <c r="B32" s="44" t="n">
+        <v>327.9</v>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>＋181.2％</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>原資料が推奨する水準</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>総括原価ベース（資産維持率3％）</t>
+        </is>
+      </c>
+      <c r="B33" s="45" t="n">
+        <v>355.3</v>
+      </c>
+      <c r="C33" s="28" t="inlineStr">
+        <is>
+          <t>＋204.7％</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>日本水道協会要領の標準</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>★【実務上の含意】資産維持率1％でも必要改定率は＋157.6％（20㎥家庭料金 2,475円→6,377円）です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 総括原価ベースの料金回収率100％を計画期間内に達成することは、現実的には困難と考えられます。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>※ 総括原価ベース（見直し後）300.4円は、令和７年度の経営比較分析表ベース332.50円と平常時ベース206.80円の間に位置し、整合的です。</t>
+          <t xml:space="preserve">　 経営戦略の目標は「計画期間内に料金回収率100％」ではなく、段階改定によって到達可能な水準（例：経常収支比率100％／料金回収率70％）に設定することを推奨します。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 将来は減価償却費と新規債利息が増える一方、江島海底送水管の応急給水費用がなくなるためです。</t>
+          <t>★ 資産維持率の選択が必要改定率に与える影響は、1％→3％で＋157.6％→＋204.7％（47.1ポイント）です。</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>【訂正】当方が令和８年８月３日にお伝えした必要改定率＋122.8％は誤りでした。総括原価の年平均を令和７年度の給水収益で除していましたが、</t>
+          <t xml:space="preserve">　 下水道事業経営戦略（案）は「収支不足補てんに伴う基準外繰入金を計上している状態であるため、現状では資産維持費を加味していません」としています。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　　　両者は有収水量の前提が異なります。分子と分母を同じ有収水量ベースで揃えると、上表のとおり＋141.6〜187.2％となります。</t>
+          <t xml:space="preserve">　 水道も繰出基準外の他会計補助金166,434千円を受けている状態ですので、資産維持費を算入する場合はその理由の説明が必要です。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A37:H37"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A23:H23"/>
     <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E75B6"/>
@@ -3220,7 +3782,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>５　原資料の要修正箇所</t>
+          <t>６　原資料の要修正箇所</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3841,7 @@
           <t>★財政シミュ Row16 の令和８〜12年度の値 ▲1,556,820千円に差替。総括原価が約111万千円増える</t>
         </is>
       </c>
-      <c r="E5" s="40" t="inlineStr">
+      <c r="E5" s="46" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>
@@ -3306,7 +3868,7 @@
           <t>★年度別の値に修正（R9:491,105／R10:500,092／R11:504,979／R12:507,209）。正しい5年合計は2,462,569千円</t>
         </is>
       </c>
-      <c r="E6" s="40" t="inlineStr">
+      <c r="E6" s="46" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>
@@ -3333,7 +3895,7 @@
           <t>No.2の修正により給水原価570.6円・料金回収率22％となる（現設定1.0％の場合）。【C】感度分析は正しく計算されている</t>
         </is>
       </c>
-      <c r="E7" s="40" t="inlineStr">
+      <c r="E7" s="46" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>
@@ -3387,7 +3949,7 @@
           <t>★どれを正式とするか決定。要領標準は3％だが、原資料は「改定率が大きくなりすぎない範囲」として1.5〜2.0％を推奨している</t>
         </is>
       </c>
-      <c r="E9" s="40" t="inlineStr">
+      <c r="E9" s="46" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>
@@ -3414,7 +3976,7 @@
           <t>★7年前の値。令和７年度決算で固定資産の計上誤りが大幅に修正されているため、R7末の固定資産台帳で再集計が必要</t>
         </is>
       </c>
-      <c r="E10" s="40" t="inlineStr">
+      <c r="E10" s="46" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>
@@ -3495,7 +4057,7 @@
           <t>★116.61円（税抜）／332.50円（R7経営比較分析表）／35.07％（R7）に差替。シート02の使い分け表に従う</t>
         </is>
       </c>
-      <c r="E13" s="40" t="inlineStr">
+      <c r="E13" s="46" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>

--- a/onagawa/output/女川町_水道_数値定義と確定値一覧.xlsx
+++ b/onagawa/output/女川町_水道_数値定義と確定値一覧.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_指標の算式と値" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_有収水量推計の見直し" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_対象資産の算定" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_総括原価の検証と再計算" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_総括原価の算定" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_原資料の要修正箇所" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -143,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -259,6 +259,9 @@
     <xf numFmtId="165" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -271,10 +274,10 @@
     <xf numFmtId="4" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2049,15 +2052,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -2070,7 +2073,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>経営戦略（案）の推計方法と令和７年度実績との乖離</t>
+          <t>料金算定対象期間：令和９年度〜令和13年度（料金改定の施行を令和９年度からと想定）</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2229,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>■【採用】見直し案Ａ　＝　給水人口 × 489.26L　（料金算定対象期間 R8〜R12）</t>
+          <t>■【採用】見直し案Ａ　＝　給水人口 × 489.26L　（料金算定対象期間 令和９〜13年度）</t>
         </is>
       </c>
     </row>
@@ -2246,11 +2249,16 @@
           <t>有収水量（㎥）</t>
         </is>
       </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>料金算定対象</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>令和8年度</t>
+          <t>令和８年度</t>
         </is>
       </c>
       <c r="B14" s="16" t="n">
@@ -2259,11 +2267,16 @@
       <c r="C14" s="16" t="n">
         <v>1004512</v>
       </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>－ 期首年度</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>令和9年度</t>
+          <t>令和９年度</t>
         </is>
       </c>
       <c r="B15" s="17" t="n">
@@ -2272,6 +2285,11 @@
       <c r="C15" s="17" t="n">
         <v>982388</v>
       </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>○ 算定対象</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
@@ -2285,6 +2303,11 @@
       <c r="C16" s="16" t="n">
         <v>960264</v>
       </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>○ 算定対象</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
@@ -2298,6 +2321,11 @@
       <c r="C17" s="17" t="n">
         <v>938140</v>
       </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>○ 算定対象</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="13" t="inlineStr">
@@ -2311,324 +2339,293 @@
       <c r="C18" s="16" t="n">
         <v>916016</v>
       </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>○ 算定対象</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
-        <is>
-          <t>5年計</t>
-        </is>
-      </c>
-      <c r="B19" s="22" t="inlineStr"/>
-      <c r="C19" s="31" t="n">
-        <v>4801318</v>
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>令和13年度</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>5006</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>893892</v>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>○ 算定対象</t>
+        </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>（参考）経営戦略（案）5年計</t>
-        </is>
-      </c>
-      <c r="B20" s="28" t="inlineStr"/>
-      <c r="C20" s="20" t="n">
-        <v>4316000</v>
-      </c>
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>★5年計（令和９〜13年度）</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr"/>
+      <c r="C20" s="31" t="n">
+        <v>4690698</v>
+      </c>
+      <c r="D20" s="23" t="inlineStr"/>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>※ 5年計 4,801,318㎥。経営戦略（案）の4,316,000㎥に対し ＋11.2％。</t>
+          <t>【なぜ見直し案Ａを採用したか】</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="4" t="inlineStr"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>① 経営戦略（案）の439.0L／人日は過去10年平均で、震災復興期（有収水量が低く、復興作業員により給水人口が多かった時期）を含みます。</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>【なぜ見直し案Ａを採用したか】</t>
+          <t xml:space="preserve">　 直近3か年の実績は484.0〜496.3Lで、案の前提を10％以上上回っています。案の令和８年度推計901千㎥は令和７年度実績1,024,576㎥を12％下回ります。</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>① 経営戦略（案）の439.0L／人日は過去10年平均で、震災復興期（有収水量が低く、復興作業員により給水人口が多かった時期）を含みます。</t>
+          <t>② 有収水量の実績はR2〜R7の6年間で1,020〜1,053千㎥とほぼ横ばいです（年▲0.1％程度）。案の想定は実績の推移と整合しません。</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 直近3か年の実績は484.0〜496.3Lで、案の前提を10％以上上回っています。令和８年度の推計901千㎥は令和７年度実績1,024,576㎥を12％下回り、初年度から実績と乖離します。</t>
+          <t>③ 総務省マニュアルの標準的手法（給水人口 × 1人1日あたり有収水量）の枠組みを維持し、基礎数値だけを直近実績に差し替える方式のため、</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>② 有収水量の実績はR2〜R7の6年間で1,020〜1,053千㎥とほぼ横ばいです（年▲0.1％程度）。案の「R6の1,019千㎥からR8に901千㎥へ11.6％減」という想定は、実績の推移と整合しません。</t>
+          <t xml:space="preserve">　 経営戦略（案）本文の修正が最小で済み、令和８年９月末の中間報告に間に合います。</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>③ 総務省マニュアルの標準的手法（給水人口 × 1人1日あたり有収水量）の枠組みを維持し、基礎数値だけを直近実績に差し替える方式のため、</t>
-        </is>
-      </c>
+      <c r="A28" s="4" t="inlineStr"/>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 経営戦略（案）本文の修正が最小で済み、令和８年９月末の中間報告に間に合います。</t>
+          <t>【採用しなかった案】用途別推計（家事用は給水人口比例、非家事用は別トレンド）… 理論的には最も妥当ですが、非家事用（有収水量の55.5％）の</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="4" t="inlineStr"/>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　トレンド設定に水産加工業の生産動向・事業所数の見通しが必要で、中間報告までに確定できません。次期の経営戦略改定時の移行を推奨します。</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>【採用しなかった案と、その理由】</t>
-        </is>
-      </c>
+      <c r="A31" s="4" t="inlineStr"/>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>・用途別推計（家事用は給水人口比例、非家事用は別トレンド）… 理論的には最も妥当ですが、非家事用（有収水量の55.5％）のトレンド設定に</t>
+          <t>【案Ａの限界（本文に注記すべき事項）】案Ａは有収水量の全量に給水人口の減少率を適用します。非家事用（55.5％）は給水人口に連動しないため、</t>
         </is>
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 水産加工業の生産動向・事業所数の見通しが必要で、中間報告までに確定できません。次期の経営戦略改定時に移行することを推奨します。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>【案Ａの限界（本文に注記すべき事項）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>・案Ａは有収水量の全量に給水人口の減少率を適用します。実際には非家事用（55.5％）は給水人口に連動しないため、</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　 非家事用が横ばいで推移する場合には過小推計となります。この意味で案Ａは保守的（原価を高めに、改定率を高めに見積もる）側の推計です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+          <t xml:space="preserve">　非家事用が横ばいで推移する場合は過小推計となります。この意味で案Ａは保守的（原価を高めに、改定率を高めに見積もる）側の推計です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>■　用途区分別の有収水量シェア　－　給水人口比例が成り立つのは44.5％だけ</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
+    <row r="36" ht="28" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>用途区分</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>水量（㎥／月）</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>シェア（％）</t>
         </is>
       </c>
     </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>家事用</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="n">
+        <v>2471</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>34668</v>
+      </c>
+      <c r="D37" s="34" t="n">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>工業用</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="n">
+        <v>66</v>
+      </c>
+      <c r="C38" s="20" t="n">
+        <v>28067</v>
+      </c>
+      <c r="D38" s="35" t="n">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>団体用</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="n">
+        <v>195</v>
+      </c>
+      <c r="C39" s="16" t="n">
+        <v>7498</v>
+      </c>
+      <c r="D39" s="36" t="n">
+        <v>9.6</v>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>営業用</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>298</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>6908</v>
+      </c>
+      <c r="D40" s="37" t="n">
+        <v>8.9</v>
+      </c>
+    </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="21" t="inlineStr">
-        <is>
-          <t>家事用</t>
-        </is>
-      </c>
-      <c r="B41" s="31" t="n">
-        <v>2471</v>
-      </c>
-      <c r="C41" s="31" t="n">
-        <v>34668</v>
-      </c>
-      <c r="D41" s="34" t="n">
-        <v>44.5</v>
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>湯屋用</t>
+        </is>
+      </c>
+      <c r="B41" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>662</v>
+      </c>
+      <c r="D41" s="36" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>工業用</t>
-        </is>
-      </c>
-      <c r="B42" s="20" t="n">
-        <v>66</v>
-      </c>
-      <c r="C42" s="20" t="n">
-        <v>28067</v>
-      </c>
-      <c r="D42" s="35" t="n">
-        <v>36.1</v>
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>臨時用</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="D42" s="37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>団体用</t>
+          <t>委託船舶給水用</t>
         </is>
       </c>
       <c r="B43" s="16" t="n">
-        <v>195</v>
+        <v>1</v>
       </c>
       <c r="C43" s="16" t="n">
-        <v>7498</v>
+        <v>11</v>
       </c>
       <c r="D43" s="36" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>営業用</t>
+          <t>合　計</t>
         </is>
       </c>
       <c r="B44" s="17" t="n">
-        <v>298</v>
+        <v>3059</v>
       </c>
       <c r="C44" s="17" t="n">
-        <v>6908</v>
+        <v>77847</v>
       </c>
       <c r="D44" s="37" t="n">
-        <v>8.9</v>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="13" t="inlineStr">
-        <is>
-          <t>湯屋用</t>
-        </is>
-      </c>
-      <c r="B45" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="C45" s="16" t="n">
-        <v>662</v>
-      </c>
-      <c r="D45" s="36" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>臨時用</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="n">
-        <v>26</v>
-      </c>
-      <c r="C46" s="17" t="n">
-        <v>33</v>
-      </c>
-      <c r="D46" s="37" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="13" t="inlineStr">
-        <is>
-          <t>委託船舶給水用</t>
-        </is>
-      </c>
-      <c r="B47" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="D47" s="36" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="15" t="inlineStr">
-        <is>
-          <t>合　計</t>
-        </is>
-      </c>
-      <c r="B48" s="17" t="n">
-        <v>3059</v>
-      </c>
-      <c r="C48" s="17" t="n">
-        <v>77847</v>
-      </c>
-      <c r="D48" s="37" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>※ 調定データ（1か月分3,060件）より集計。家事用は44.5％にすぎず、工業用が36.1％をわずか66件（大半が水産加工業）で占めています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>※ なお給水人口の推計値（令和８年度5,625人）は令和７年度実績5,656人と整合しており、差し替えは不要です。</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="23">
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A50:F50"/>
-    <mergeCell ref="A26:F26"/>
+  <mergeCells count="17">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A4:F4"/>
     <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2642,22 +2639,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>４　資産維持費の対象資産の算定　－　料金算定対象期間（R8〜R12）の平均</t>
+          <t>４　資産維持費の対象資産　－　料金算定対象期間（令和９〜13年度）の平均</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2782,7 @@
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>★ 従前の試算で用いていた対象資産1,042,625,176円は、試算シート記載のH31（令和元年度）末帳簿価額（取水124,491,503＋浄水157,489,766＋配水760,643,907）でした。</t>
+          <t>★ 従前の試算で用いていた対象資産1,042,625,176円は、試算シート記載のH31（令和元年度）末帳簿価額でした。</t>
         </is>
       </c>
     </row>
@@ -2796,319 +2793,383 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　 令和７年度決算で減価償却累計額等が大幅に修正されているため、令和７年度末の明細書を起点としました。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>■　(2) 料金算定対象期間の推移</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>■　(2) 料金算定対象期間の推移　－　期首は令和８年度末、期末は令和13年度末</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>年　度</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>定義Ａ 償却資産</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>長期前受金残高</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
         <is>
           <t>★定義Ｂ 対象資産</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>当年度取得（税抜）</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>当年度減価償却費</t>
         </is>
       </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>区　分</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>令和７年度末</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>9083572422</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>7491683492</v>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>1591888930</v>
+      </c>
+      <c r="E18" s="26" t="inlineStr"/>
+      <c r="F18" s="26" t="inlineStr"/>
+      <c r="G18" s="13" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>令和７年度末（期首）</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n">
-        <v>9083572422</v>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>7491683492</v>
-      </c>
-      <c r="D19" s="16" t="n">
-        <v>1591888930</v>
-      </c>
-      <c r="E19" s="26" t="inlineStr"/>
-      <c r="F19" s="26" t="inlineStr"/>
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>令和８年度末</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="n">
+        <v>9624668749</v>
+      </c>
+      <c r="C19" s="31" t="n">
+        <v>7228067464</v>
+      </c>
+      <c r="D19" s="31" t="n">
+        <v>2396601285</v>
+      </c>
+      <c r="E19" s="31" t="n">
+        <v>936363636</v>
+      </c>
+      <c r="F19" s="31" t="n">
+        <v>395267309</v>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>★期首（料金算定対象期間の期首）</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>令和８年度末</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n">
-        <v>9624668749</v>
-      </c>
-      <c r="C20" s="17" t="n">
-        <v>7228067464</v>
-      </c>
-      <c r="D20" s="17" t="n">
-        <v>2396601285</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>936363636</v>
-      </c>
-      <c r="F20" s="17" t="n">
-        <v>395267309</v>
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>令和９年度末</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n">
+        <v>10073382025</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>6956197363</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>3117184662</v>
+      </c>
+      <c r="E20" s="16" t="n">
+        <v>863636364</v>
+      </c>
+      <c r="F20" s="16" t="n">
+        <v>414923088</v>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>算定対象期間内</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>令和９年度末</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n">
-        <v>10073382025</v>
-      </c>
-      <c r="C21" s="16" t="n">
-        <v>6956197363</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>3117184662</v>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>863636364</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>414923088</v>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>令和10年度末</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>10115063910</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>6697332623</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>3417731287</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>454545455</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>412863570</v>
+      </c>
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>算定対象期間内</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>令和10年度末</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n">
-        <v>10115063910</v>
-      </c>
-      <c r="C22" s="17" t="n">
-        <v>6697332623</v>
-      </c>
-      <c r="D22" s="17" t="n">
-        <v>3417731287</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>454545455</v>
-      </c>
-      <c r="F22" s="17" t="n">
-        <v>412863570</v>
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>令和11年度末</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>10007910044</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>6450347090</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>3557562954</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>407153866</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>算定対象期間内</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>令和11年度末</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n">
-        <v>10007910044</v>
-      </c>
-      <c r="C23" s="16" t="n">
-        <v>6450347090</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>3557562954</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>300000000</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>407153866</v>
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>令和12年度末</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>9887493862</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>6213193354</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>3674300508</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>281818182</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>402234363</v>
+      </c>
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>算定対象期間内</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>令和12年度末</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n">
-        <v>9887493862</v>
-      </c>
-      <c r="C24" s="17" t="n">
-        <v>6213193354</v>
-      </c>
-      <c r="D24" s="17" t="n">
-        <v>3674300508</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>281818182</v>
-      </c>
-      <c r="F24" s="17" t="n">
-        <v>402234363</v>
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>令和13年度末</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="n">
+        <v>9770429405</v>
+      </c>
+      <c r="C24" s="31" t="n">
+        <v>5932379517</v>
+      </c>
+      <c r="D24" s="31" t="n">
+        <v>3838049888</v>
+      </c>
+      <c r="E24" s="31" t="n">
+        <v>282727273</v>
+      </c>
+      <c r="F24" s="31" t="n">
+        <v>399791730</v>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>★期末（同 期末）</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
-        <is>
-          <t>★期首期末平均</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="n">
-        <v>9485533142</v>
-      </c>
-      <c r="C25" s="31" t="n">
-        <v>6852438423</v>
-      </c>
-      <c r="D25" s="31" t="n">
-        <v>2633094719</v>
-      </c>
-      <c r="E25" s="22" t="inlineStr"/>
-      <c r="F25" s="22" t="inlineStr"/>
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>★期首期末平均（R8末・R13末）</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="n">
+        <v>9697549077</v>
+      </c>
+      <c r="C25" s="18" t="n">
+        <v>6580223490</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>3117325587</v>
+      </c>
+      <c r="E25" s="27" t="inlineStr"/>
+      <c r="F25" s="27" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr">
+        <is>
+          <t>日本水道協会「水道料金算定要領」の方式</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>（参考）各年度平均</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="n">
-        <v>9798681835</v>
-      </c>
-      <c r="C26" s="17" t="n">
-        <v>6839470231</v>
-      </c>
-      <c r="D26" s="17" t="n">
-        <v>2959211604</v>
-      </c>
-      <c r="E26" s="25" t="inlineStr"/>
-      <c r="F26" s="25" t="inlineStr"/>
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>（参考）各年度平均（R8末〜R13末）</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n">
+        <v>9913157999</v>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>6579586235</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>3333571764</v>
+      </c>
+      <c r="E26" s="26" t="inlineStr"/>
+      <c r="F26" s="26" t="inlineStr"/>
+      <c r="G26" s="13" t="inlineStr"/>
     </row>
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>※ 取得額は財政シミュの建設改良費（税込）を1.1で除した税抜相当額。長期前受金の増加は国庫補助金＋他会計補助金（出資金は資本金であり長期前受金にならない）。</t>
+          <t>※ 取得額は財政シミュの建設改良費（原水及び浄水施設費＋送水及び配水施設費・税込）を1.1で除した税抜相当額。</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>※ 定義Ｂが期間中に1,592百万円→3,674百万円と増えるのは、令和８年度以降の投資（5年計 税抜2,836百万円）の財源が</t>
+          <t>※ 長期前受金の増加は国庫補助金＋他会計補助金（出資金は資本金であり長期前受金にならない）。令和13年度は国庫補助金の計上がないため3,000千円のみ。</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 企業債1,712百万円＋出資金1,130百万円で、補助金は275百万円にとどまるためです。復興期（補助金中心）からの構造変化が表れています。</t>
+          <t>★ 料金改定の施行を令和９年度からと想定し、料金算定対象期間を令和９〜13年度としています。したがって期首は令和８年度末です。</t>
         </is>
       </c>
     </row>
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>★ 料金算定対象期間の平均は、日本水道協会「水道料金算定要領」に従い期首期末平均を採用しました（各年度平均も併記）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+          <t>※ 対象資産が期間中に2,397百万円→3,838百万円と増えるのは、令和８年度以降の投資の財源が企業債・出資金中心で、補助金が限られるためです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 復興期（補助金中心）からの構造変化が表れています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>■　(3) 対象資産の定義について</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="6" t="inlineStr">
+    <row r="35" ht="28" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>定　義</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>期首期末平均</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>3％の場合の年額</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>給水収益に対する比</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>評　価</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="46" customHeight="1">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36" ht="46" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>定義Ａ　償却資産の帳簿価額（要領の文言どおり）</t>
         </is>
       </c>
-      <c r="B35" s="20" t="n">
-        <v>9485533142</v>
-      </c>
-      <c r="C35" s="20" t="n">
-        <v>284565994</v>
-      </c>
-      <c r="D35" s="28" t="inlineStr">
-        <is>
-          <t>238％</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>★女川町は資産の82％が補助金等で取得されているため、この定義では資産維持費が給水収益の2.4倍となり実務的でない</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="46" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="B36" s="20" t="n">
+        <v>9697549077</v>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>290926472</v>
+      </c>
+      <c r="D36" s="28" t="inlineStr">
+        <is>
+          <t>243％</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>★女川町は資産の8割超が補助金等で取得されているため、この定義では資産維持費が給水収益の2倍を超え実務的でない</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="46" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
         <is>
           <t>★定義Ｂ　償却資産 − 長期前受金（採用）</t>
         </is>
       </c>
-      <c r="B36" s="31" t="n">
-        <v>2633094719</v>
-      </c>
-      <c r="C36" s="31" t="n">
-        <v>78992842</v>
-      </c>
-      <c r="D36" s="22" t="inlineStr">
-        <is>
-          <t>66％</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="B37" s="31" t="n">
+        <v>3117325587</v>
+      </c>
+      <c r="C37" s="31" t="n">
+        <v>93519768</v>
+      </c>
+      <c r="D37" s="22" t="inlineStr">
+        <is>
+          <t>78％</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>総括原価で長期前受金戻入益を控除していることと整合する。自己財源で更新すべき資産に対応</t>
         </is>
@@ -3116,17 +3177,17 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A32:G32"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A34:G34"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A33:G33"/>
     <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3140,37 +3201,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>５　総括原価の検証と再計算</t>
+          <t>５　総括原価の算定　－　料金算定対象期間（令和９〜13年度）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>原資料：onagawa_tariff_cost_calc.xlsx ②総括原価の算定／onagawa_cost_sim_v1.xlsx／経営戦略試算シート【成行】財政シミュ</t>
+          <t>将来の料金算定対象期間の原価を料金で賄う形で算定。原資料：onagawa_tariff_cost_calc.xlsx／onagawa_cost_sim_v1.xlsx／【成行】財政シミュ</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>■　(1) 財政シミュとの照合　－　長期前受金戻入益だけが未反映</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>■　(1) 費目別の原価（令和９〜13年度・円）</t>
         </is>
       </c>
     </row>
@@ -3182,27 +3243,27 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R11</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>R11</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R13</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
@@ -3212,343 +3273,412 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>照合結果</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
+          <t>備　考</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="13" t="inlineStr">
         <is>
           <t>維持管理費（営業費用−減価償却費）</t>
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>131926</v>
+        <v>133182550</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>133182</v>
+        <v>134453325</v>
       </c>
       <c r="D6" s="16" t="n">
-        <v>134453</v>
+        <v>135741651</v>
       </c>
       <c r="E6" s="16" t="n">
-        <v>135742</v>
+        <v>137024012</v>
       </c>
       <c r="F6" s="16" t="n">
-        <v>137024</v>
+        <v>138341171</v>
       </c>
       <c r="G6" s="16" t="n">
-        <v>672327</v>
-      </c>
-      <c r="H6" s="13" t="inlineStr">
-        <is>
-          <t>○ 原資料と一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+        <v>678742709</v>
+      </c>
+      <c r="H6" s="13" t="inlineStr"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
           <t>減価償却費（財政シミュ Row52）</t>
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>395267</v>
+        <v>414923088</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>414923</v>
+        <v>412863570</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>412864</v>
+        <v>407153866</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>407154</v>
+        <v>402234363</v>
       </c>
       <c r="F7" s="17" t="n">
-        <v>402234</v>
+        <v>399791730</v>
       </c>
       <c r="G7" s="17" t="n">
-        <v>2032442</v>
-      </c>
-      <c r="H7" s="15" t="inlineStr">
-        <is>
-          <t>○ 一致（原資料2,032,440。丸め差2千円）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+        <v>2036966617</v>
+      </c>
+      <c r="H7" s="15" t="inlineStr"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="13" t="inlineStr">
         <is>
           <t>支払利息 既往債（同 Row60）</t>
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>10790</v>
+        <v>10529945</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>10530</v>
+        <v>10171513</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>10172</v>
+        <v>9805314</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>9805</v>
+        <v>9287703</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>9288</v>
+        <v>8710700</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>50585</v>
-      </c>
-      <c r="H8" s="13" t="inlineStr">
-        <is>
-          <t>○ 一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
+        <v>48505175</v>
+      </c>
+      <c r="H8" s="13" t="inlineStr"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
           <t>支払利息 新規債（同 Row61）</t>
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>9238</v>
+        <v>18507390</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>18507</v>
+        <v>26640850</v>
       </c>
       <c r="D9" s="17" t="n">
-        <v>26641</v>
+        <v>34316071</v>
       </c>
       <c r="E9" s="17" t="n">
-        <v>34316</v>
+        <v>38700148</v>
       </c>
       <c r="F9" s="17" t="n">
-        <v>38700</v>
+        <v>42991146</v>
       </c>
       <c r="G9" s="17" t="n">
-        <v>127402</v>
-      </c>
-      <c r="H9" s="15" t="inlineStr">
-        <is>
-          <t>○ 一致</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+        <v>161155605</v>
+      </c>
+      <c r="H9" s="15" t="inlineStr"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>★長期前受金戻入益（同 Row16）</t>
+          <t>★控除　長期前受金戻入益（同 Row16）</t>
         </is>
       </c>
       <c r="B10" s="20" t="n">
-        <v>-329946</v>
+        <v>-324870101</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>-324870</v>
+        <v>-311864740</v>
       </c>
       <c r="D10" s="20" t="n">
-        <v>-311865</v>
+        <v>-299985533</v>
       </c>
       <c r="E10" s="20" t="n">
-        <v>-299986</v>
+        <v>-290153736</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-290154</v>
+        <v>-283813837</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-1556820</v>
+        <v>-1510687947</v>
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>× 原資料は▲450,000千円（3.46倍の差）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>★ 原資料の備考には「（推計値）財政シミュR6〜R7平均から推計。要精査。」と明記されています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　 ただし財政シミュのR6は334,202千円、R7は334,252千円で、その平均から5年分を推計しても約1,671,000千円となり、450,000千円にはなりません。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>★ 他の4費目はすべて財政シミュの値と一致しています。長期前受金戻入益だけが置き換えられないまま残ったプレースホルダと判断されます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>■　(2) 総括原価と必要改定率（資産維持率 1％・2％・3％）</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
+          <t>原資料は▲450,000千円（R8〜R12）のプレースホルダのまま</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>控除　他会計補助金等</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="C11" s="17" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="F11" s="17" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="G11" s="17" t="n">
+        <v>-15000000</v>
+      </c>
+      <c r="H11" s="15" t="inlineStr"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>差引（資産維持費前）</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr"/>
+      <c r="C12" s="22" t="inlineStr"/>
+      <c r="D12" s="22" t="inlineStr"/>
+      <c r="E12" s="22" t="inlineStr"/>
+      <c r="F12" s="22" t="inlineStr"/>
+      <c r="G12" s="31" t="n">
+        <v>1399682159</v>
+      </c>
+      <c r="H12" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>■　(2) 総括原価と必要改定率（資産維持率 1.0％〜3.0％）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>資産維持率</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>対象資産
-（期首期末平均・千円）</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
+（期首期末平均・円）</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>資産維持費
-5年計（千円）</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
+5年計（円）</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>総括原価
-5年計（千円）</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
+5年計（円）</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>給水原価
 （円/㎥）</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>必要改定率</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>現行の料金回収率
 （％）</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H15" s="6" t="inlineStr">
         <is>
           <t>20㎥家庭料金
 （改定後・税込）</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>1％</t>
-        </is>
-      </c>
-      <c r="B18" s="31" t="n">
-        <v>2633095</v>
-      </c>
-      <c r="C18" s="31" t="n">
-        <v>131655</v>
-      </c>
-      <c r="D18" s="31" t="n">
-        <v>1442591</v>
-      </c>
-      <c r="E18" s="38" t="n">
-        <v>300.5</v>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>＋157.6％</t>
-        </is>
-      </c>
-      <c r="G18" s="34" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="H18" s="22" t="inlineStr">
-        <is>
-          <t>6,377円</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t>2％</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="n">
-        <v>2633095</v>
-      </c>
-      <c r="C19" s="18" t="n">
-        <v>263309</v>
-      </c>
-      <c r="D19" s="18" t="n">
-        <v>1574245</v>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>1.0％</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="n">
+        <v>3117325587</v>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>155866279</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>1555548438</v>
+      </c>
+      <c r="E16" s="38" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>＋184.4％</t>
+        </is>
+      </c>
+      <c r="G16" s="34" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t>7,038円</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>1.5％</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n">
+        <v>3117325587</v>
+      </c>
+      <c r="C17" s="17" t="n">
+        <v>233799419</v>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>1633481578</v>
+      </c>
+      <c r="E17" s="39" t="n">
+        <v>348.2</v>
+      </c>
+      <c r="F17" s="25" t="inlineStr">
+        <is>
+          <t>＋198.6％</t>
+        </is>
+      </c>
+      <c r="G17" s="37" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>7,391円</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>2.0％</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>3117325587</v>
+      </c>
+      <c r="C18" s="18" t="n">
+        <v>311732559</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>1711414718</v>
+      </c>
+      <c r="E18" s="40" t="n">
+        <v>364.9</v>
+      </c>
+      <c r="F18" s="27" t="inlineStr">
+        <is>
+          <t>＋212.9％</t>
+        </is>
+      </c>
+      <c r="G18" s="41" t="n">
+        <v>32</v>
+      </c>
+      <c r="H18" s="27" t="inlineStr">
+        <is>
+          <t>7,744円</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>2.5％</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>3117325587</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>389665698</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>1789347857</v>
       </c>
       <c r="E19" s="39" t="n">
-        <v>327.9</v>
-      </c>
-      <c r="F19" s="27" t="inlineStr">
-        <is>
-          <t>＋181.2％</t>
-        </is>
-      </c>
-      <c r="G19" s="40" t="n">
-        <v>35.6</v>
-      </c>
-      <c r="H19" s="27" t="inlineStr">
-        <is>
-          <t>6,959円</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
+        <v>381.5</v>
+      </c>
+      <c r="F19" s="25" t="inlineStr">
+        <is>
+          <t>＋227.1％</t>
+        </is>
+      </c>
+      <c r="G19" s="37" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="H19" s="25" t="inlineStr">
+        <is>
+          <t>8,096円</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>3％</t>
+          <t>3.0％</t>
         </is>
       </c>
       <c r="B20" s="20" t="n">
-        <v>2633095</v>
+        <v>3117325587</v>
       </c>
       <c r="C20" s="20" t="n">
-        <v>394964</v>
+        <v>467598838</v>
       </c>
       <c r="D20" s="20" t="n">
-        <v>1705900</v>
-      </c>
-      <c r="E20" s="41" t="n">
-        <v>355.3</v>
+        <v>1867280997</v>
+      </c>
+      <c r="E20" s="42" t="n">
+        <v>398.1</v>
       </c>
       <c r="F20" s="28" t="inlineStr">
         <is>
-          <t>＋204.7％</t>
+          <t>＋241.4％</t>
         </is>
       </c>
       <c r="G20" s="35" t="n">
-        <v>32.8</v>
+        <v>29.3</v>
       </c>
       <c r="H20" s="28" t="inlineStr">
         <is>
-          <t>7,541円</t>
+          <t>8,449円</t>
         </is>
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>※ 基礎費用（維持管理費＋減価償却費＋既往債利息＋新規債利息）2,882,756千円、控除（長期前受金戻入益▲1,556,820＋他会計補助金等▲15,000）-1,571,820千円。</t>
+          <t>※ 差引（資産維持費前）1,399,682,159円 ＋ 資産維持費（対象資産3,117,325,587円 × 資産維持率 × 5年）。</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>※ 有収水量は見直し案Ａの5年計 4,801,318㎥（シート03）。対象資産は定義Ｂの期首期末平均 2,633,094,719円（シート04）。</t>
+          <t>※ 有収水量5年計（令和９〜13年度）4,690,698㎥（シート03）。</t>
         </is>
       </c>
     </row>
@@ -3566,127 +3696,114 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>※ 資産維持率の選択が必要改定率に与える影響は、1.0％→3.0％で57.0ポイントです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>■　(3) 他の算定基準との整合と、実務上の含意</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>基　準</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>給水原価（円/㎥）</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>必要改定率</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>位置づけ</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>令和７年度 平常時ベース（一過性を除く）</t>
         </is>
       </c>
-      <c r="B29" s="42" t="n">
+      <c r="B30" s="43" t="n">
         <v>206.8</v>
       </c>
-      <c r="C29" s="26" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>＋77.3％</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>現状維持の下限。将来の投資を含まない</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
-        <is>
-          <t>★総括原価ベース（資産維持率1％）</t>
-        </is>
-      </c>
-      <c r="B30" s="43" t="n">
-        <v>300.5</v>
-      </c>
-      <c r="C30" s="22" t="inlineStr">
-        <is>
-          <t>＋157.6％</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>将来の投資を織り込んだ最小水準</t>
-        </is>
-      </c>
-    </row>
     <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>令和７年度 経営比較分析表ベース</t>
         </is>
       </c>
-      <c r="B31" s="42" t="n">
+      <c r="B31" s="44" t="n">
         <v>332.5</v>
       </c>
-      <c r="C31" s="26" t="inlineStr">
+      <c r="C31" s="25" t="inlineStr">
         <is>
           <t>＋185.1％</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>江島の一過性費用を料金で回収する場合</t>
         </is>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>総括原価ベース（資産維持率2％）</t>
-        </is>
-      </c>
-      <c r="B32" s="44" t="n">
-        <v>327.9</v>
-      </c>
-      <c r="C32" s="27" t="inlineStr">
-        <is>
-          <t>＋181.2％</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>原資料が推奨する水準</t>
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>★総括原価ベース（資産維持率1.0％）</t>
+        </is>
+      </c>
+      <c r="B32" s="45" t="n">
+        <v>331.6</v>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>＋184.4％</t>
+        </is>
+      </c>
+      <c r="D32" s="21" t="inlineStr">
+        <is>
+          <t>将来の投資と更新財源を織り込んだ最小水準</t>
         </is>
       </c>
     </row>
     <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>総括原価ベース（資産維持率3％）</t>
-        </is>
-      </c>
-      <c r="B33" s="45" t="n">
-        <v>355.3</v>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>★総括原価ベース（資産維持率3.0％）</t>
+        </is>
+      </c>
+      <c r="B33" s="46" t="n">
+        <v>398.1</v>
       </c>
       <c r="C33" s="28" t="inlineStr">
         <is>
-          <t>＋204.7％</t>
+          <t>＋241.4％</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
@@ -3698,63 +3815,69 @@
     <row r="35" ht="16" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>★【実務上の含意】資産維持率1％でも必要改定率は＋157.6％（20㎥家庭料金 2,475円→6,377円）です。</t>
+          <t>★【実務上の含意】資産維持率1.0％でも必要改定率は＋184.4％（20㎥家庭料金 2,475円→7,038円）です。</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 総括原価ベースの料金回収率100％を計画期間内に達成することは、現実的には困難と考えられます。</t>
+          <t xml:space="preserve">　 総括原価ベースの料金回収率100％を一度の改定で達成することは、現実的には困難と考えられます。</t>
         </is>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 経営戦略の目標は「計画期間内に料金回収率100％」ではなく、段階改定によって到達可能な水準（例：経常収支比率100％／料金回収率70％）に設定することを推奨します。</t>
+          <t xml:space="preserve">　 経営戦略の目標は「計画期間内に料金回収率100％」ではなく、段階改定によって到達可能な水準に設定することを推奨します。</t>
         </is>
       </c>
     </row>
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>★ 資産維持率の選択が必要改定率に与える影響は、1％→3％で＋157.6％→＋204.7％（47.1ポイント）です。</t>
+          <t>※ 料金算定対象期間を令和８〜12年度とした場合と比べ、必要改定率は約27ポイント高くなります。令和13年度は国庫補助金の計上がなく、</t>
         </is>
       </c>
     </row>
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 下水道事業経営戦略（案）は「収支不足補てんに伴う基準外繰入金を計上している状態であるため、現状では資産維持費を加味していません」としています。</t>
+          <t xml:space="preserve">　 新規債利息が増え、有収水量も減るためです。算定対象期間の設定が結果に与える影響は小さくありません。</t>
         </is>
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>※ 下水道事業経営戦略（案）は「収支不足補てんに伴う基準外繰入金を計上している状態であるため、現状では資産維持費を加味していません」としています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">　 水道も繰出基準外の他会計補助金166,434千円を受けている状態ですので、資産維持費を算入する場合はその理由の説明が必要です。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A12:H12"/>
+  <mergeCells count="17">
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A40:H40"/>
   </mergeCells>
@@ -3841,7 +3964,7 @@
           <t>★財政シミュ Row16 の令和８〜12年度の値 ▲1,556,820千円に差替。総括原価が約111万千円増える</t>
         </is>
       </c>
-      <c r="E5" s="46" t="inlineStr">
+      <c r="E5" s="47" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>
@@ -3868,7 +3991,7 @@
           <t>★年度別の値に修正（R9:491,105／R10:500,092／R11:504,979／R12:507,209）。正しい5年合計は2,462,569千円</t>
         </is>
       </c>
-      <c r="E6" s="46" t="inlineStr">
+      <c r="E6" s="47" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>
@@ -3895,7 +4018,7 @@
           <t>No.2の修正により給水原価570.6円・料金回収率22％となる（現設定1.0％の場合）。【C】感度分析は正しく計算されている</t>
         </is>
       </c>
-      <c r="E7" s="46" t="inlineStr">
+      <c r="E7" s="47" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>
@@ -3949,7 +4072,7 @@
           <t>★どれを正式とするか決定。要領標準は3％だが、原資料は「改定率が大きくなりすぎない範囲」として1.5〜2.0％を推奨している</t>
         </is>
       </c>
-      <c r="E9" s="46" t="inlineStr">
+      <c r="E9" s="47" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>
@@ -3976,7 +4099,7 @@
           <t>★7年前の値。令和７年度決算で固定資産の計上誤りが大幅に修正されているため、R7末の固定資産台帳で再集計が必要</t>
         </is>
       </c>
-      <c r="E10" s="46" t="inlineStr">
+      <c r="E10" s="47" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>
@@ -4057,7 +4180,7 @@
           <t>★116.61円（税抜）／332.50円（R7経営比較分析表）／35.07％（R7）に差替。シート02の使い分け表に従う</t>
         </is>
       </c>
-      <c r="E13" s="46" t="inlineStr">
+      <c r="E13" s="47" t="inlineStr">
         <is>
           <t>★最優先</t>
         </is>
